--- a/p6_deployment/data/germany/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/p6_deployment/data/germany/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A28"/>
+  <dimension ref="A2:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -613,6 +613,34 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
